--- a/domain/demo_corpus/files/customer_data_dictionary_v1.xlsx
+++ b/domain/demo_corpus/files/customer_data_dictionary_v1.xlsx
@@ -458,7 +458,6 @@
           <t>Primary key.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
